--- a/data/HVGene_validation_dataset.xlsx
+++ b/data/HVGene_validation_dataset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Teo\AppData\Local\Temp\claude\C--Users-Teo-SynologyDrive-Obsidian-COSMIC-04-R-daction-1-Articles-generator-hardwareX\da640f6b-b219-41d1-b3af-b4334022494f\scratchpad\ds\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Teo\SynologyDrive\Obsidian_COSMIC\01_Développement\1_Générateur\HVGene_OpenHardware_repo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90AA762-F24A-415E-8A43-A11E03C96F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF8E709B-897E-441C-A5F4-F81D9D1F39E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment" sheetId="2" r:id="rId1"/>
@@ -160,9 +160,6 @@
   </si>
   <si>
     <t>Power Factor_scope</t>
-  </si>
-  <si>
-    <t>THD (%)</t>
   </si>
   <si>
     <t>V1 (Vrms)</t>
@@ -818,6 +815,9 @@
   <si>
     <t>Consistency</t>
   </si>
+  <si>
+    <t>THD (fraction)</t>
+  </si>
 </sst>
 </file>
 
@@ -1238,22 +1238,22 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1582,7 +1582,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1601,30 +1601,30 @@
         <v>22</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>107</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>108</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>110</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -1647,10 +1647,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -1673,10 +1673,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -1686,7 +1686,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>25</v>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>117</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
@@ -1725,10 +1725,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
@@ -1738,12 +1738,12 @@
     </row>
     <row r="15" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B16" s="8">
         <v>3</v>
@@ -1751,7 +1751,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B17" s="8">
         <v>5</v>
@@ -1767,7 +1767,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B19" s="8">
         <v>6</v>
@@ -1794,8 +1794,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="58" t="s">
-        <v>126</v>
+      <c r="A1" s="57" t="s">
+        <v>125</v>
       </c>
       <c r="B1" s="55"/>
       <c r="C1" s="55"/>
@@ -1842,7 +1842,7 @@
       <c r="AR1" s="55"/>
     </row>
     <row r="2" spans="1:44" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="56" t="s">
         <v>27</v>
       </c>
       <c r="B2" s="55"/>
@@ -1852,21 +1852,21 @@
       <c r="F2" s="55"/>
       <c r="G2" s="55"/>
       <c r="H2" s="55"/>
-      <c r="I2" s="57" t="s">
-        <v>127</v>
+      <c r="I2" s="56" t="s">
+        <v>126</v>
       </c>
       <c r="J2" s="55"/>
       <c r="K2" s="55"/>
       <c r="L2" s="55"/>
       <c r="M2" s="55"/>
-      <c r="N2" s="57" t="s">
-        <v>128</v>
+      <c r="N2" s="56" t="s">
+        <v>127</v>
       </c>
       <c r="O2" s="55"/>
       <c r="P2" s="55"/>
       <c r="Q2" s="55"/>
-      <c r="R2" s="57" t="s">
-        <v>129</v>
+      <c r="R2" s="56" t="s">
+        <v>128</v>
       </c>
       <c r="S2" s="55"/>
       <c r="T2" s="55"/>
@@ -1876,8 +1876,8 @@
       <c r="X2" s="55"/>
       <c r="Y2" s="55"/>
       <c r="Z2" s="55"/>
-      <c r="AA2" s="57" t="s">
-        <v>130</v>
+      <c r="AA2" s="56" t="s">
+        <v>129</v>
       </c>
       <c r="AB2" s="55"/>
       <c r="AC2" s="55"/>
@@ -1890,32 +1890,32 @@
       <c r="AJ2" s="55"/>
       <c r="AK2" s="55"/>
       <c r="AL2" s="55"/>
-      <c r="AM2" s="57" t="s">
-        <v>131</v>
+      <c r="AM2" s="56" t="s">
+        <v>130</v>
       </c>
       <c r="AN2" s="55"/>
       <c r="AO2" s="55"/>
       <c r="AP2" s="55"/>
-      <c r="AQ2" s="57" t="s">
-        <v>132</v>
+      <c r="AQ2" s="56" t="s">
+        <v>131</v>
       </c>
       <c r="AR2" s="55"/>
     </row>
     <row r="3" spans="1:44" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>133</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>134</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>28</v>
       </c>
       <c r="D3" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>135</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>136</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>29</v>
@@ -1924,7 +1924,7 @@
         <v>30</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>31</v>
@@ -1936,16 +1936,16 @@
         <v>33</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M3" s="13" t="s">
         <v>6</v>
       </c>
       <c r="N3" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="O3" s="14" t="s">
         <v>139</v>
-      </c>
-      <c r="O3" s="14" t="s">
-        <v>140</v>
       </c>
       <c r="P3" s="14" t="s">
         <v>3</v>
@@ -1969,7 +1969,7 @@
         <v>38</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="X3" s="15" t="s">
         <v>5</v>
@@ -1978,66 +1978,66 @@
         <v>39</v>
       </c>
       <c r="Z3" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA3" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="AB3" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="AA3" s="16" t="s">
+      <c r="AC3" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="AB3" s="16" t="s">
+      <c r="AD3" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE3" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF3" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG3" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH3" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI3" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="AJ3" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="AK3" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL3" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM3" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN3" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="AC3" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD3" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE3" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF3" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG3" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH3" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI3" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="AJ3" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK3" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="AL3" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AM3" s="17" t="s">
+      <c r="AO3" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="AP3" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="AQ3" s="18" t="s">
         <v>51</v>
-      </c>
-      <c r="AN3" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="AO3" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="AP3" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="AQ3" s="18" t="s">
-        <v>52</v>
       </c>
       <c r="AR3" s="18" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="59" t="s">
-        <v>147</v>
+      <c r="A4" s="54" t="s">
+        <v>146</v>
       </c>
       <c r="B4" s="55"/>
       <c r="C4" s="55"/>
@@ -2085,13 +2085,13 @@
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B5" s="19">
         <v>1</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="19">
@@ -2198,13 +2198,13 @@
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B6" s="19">
         <v>2</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="19">
@@ -2311,13 +2311,13 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B7" s="19">
         <v>3</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="19">
@@ -2430,13 +2430,13 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B8" s="19">
         <v>4</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="19">
@@ -2551,13 +2551,13 @@
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B9" s="19">
         <v>5</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="19">
@@ -2672,13 +2672,13 @@
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B10" s="19">
         <v>6</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="19">
@@ -2793,13 +2793,13 @@
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B11" s="19">
         <v>7</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="19">
@@ -2914,13 +2914,13 @@
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B12" s="19">
         <v>8</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="19">
@@ -3035,13 +3035,13 @@
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B13" s="19">
         <v>9</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="19">
@@ -3156,13 +3156,13 @@
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B14" s="19">
         <v>10</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" s="19"/>
       <c r="E14" s="19">
@@ -3276,8 +3276,8 @@
       <c r="AR14" s="19"/>
     </row>
     <row r="15" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="59" t="s">
-        <v>149</v>
+      <c r="A15" s="54" t="s">
+        <v>148</v>
       </c>
       <c r="B15" s="55"/>
       <c r="C15" s="55"/>
@@ -3325,13 +3325,13 @@
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B16" s="19">
         <v>1</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" s="19"/>
       <c r="E16" s="19">
@@ -3439,18 +3439,18 @@
       <c r="AP16" s="19"/>
       <c r="AQ16" s="19"/>
       <c r="AR16" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B17" s="19">
         <v>2</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D17" s="19"/>
       <c r="E17" s="19">
@@ -3565,13 +3565,13 @@
     </row>
     <row r="18" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B18" s="19">
         <v>3</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D18" s="19"/>
       <c r="E18" s="19">
@@ -3686,13 +3686,13 @@
     </row>
     <row r="19" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B19" s="19">
         <v>4</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D19" s="19"/>
       <c r="E19" s="19">
@@ -3804,18 +3804,18 @@
       <c r="AP19" s="19"/>
       <c r="AQ19" s="19"/>
       <c r="AR19" s="19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B20" s="19">
         <v>5</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="19">
@@ -3927,18 +3927,18 @@
       <c r="AP20" s="19"/>
       <c r="AQ20" s="19"/>
       <c r="AR20" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B21" s="19">
         <v>6</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D21" s="19"/>
       <c r="E21" s="19">
@@ -4053,13 +4053,13 @@
     </row>
     <row r="22" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B22" s="19">
         <v>7</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D22" s="19"/>
       <c r="E22" s="19">
@@ -4174,13 +4174,13 @@
     </row>
     <row r="23" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B23" s="19">
         <v>8</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D23" s="19"/>
       <c r="E23" s="19">
@@ -4295,13 +4295,13 @@
     </row>
     <row r="24" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B24" s="19">
         <v>9</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19">
@@ -4416,13 +4416,13 @@
     </row>
     <row r="25" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B25" s="19">
         <v>10</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19">
@@ -4537,13 +4537,13 @@
     </row>
     <row r="26" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B26" s="19">
         <v>11</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D26" s="19"/>
       <c r="E26" s="19">
@@ -4619,12 +4619,12 @@
       <c r="AP26" s="19"/>
       <c r="AQ26" s="19"/>
       <c r="AR26" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="27" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="54" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="27" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="59" t="s">
-        <v>155</v>
       </c>
       <c r="B27" s="55"/>
       <c r="C27" s="55"/>
@@ -4672,13 +4672,13 @@
     </row>
     <row r="28" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B28" s="19">
         <v>1</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19">
@@ -4787,13 +4787,13 @@
     </row>
     <row r="29" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A29" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B29" s="19">
         <v>2</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19">
@@ -4910,13 +4910,13 @@
     </row>
     <row r="30" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A30" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B30" s="19">
         <v>3</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19">
@@ -5033,13 +5033,13 @@
     </row>
     <row r="31" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A31" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B31" s="19">
         <v>4</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D31" s="19"/>
       <c r="E31" s="19">
@@ -5158,13 +5158,13 @@
     </row>
     <row r="32" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A32" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B32" s="19">
         <v>5</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D32" s="19"/>
       <c r="E32" s="19">
@@ -5283,13 +5283,13 @@
     </row>
     <row r="33" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A33" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B33" s="19">
         <v>6</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D33" s="19"/>
       <c r="E33" s="19">
@@ -5408,13 +5408,13 @@
     </row>
     <row r="34" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A34" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B34" s="19">
         <v>7</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D34" s="19"/>
       <c r="E34" s="19">
@@ -5533,13 +5533,13 @@
     </row>
     <row r="35" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A35" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B35" s="19">
         <v>8</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D35" s="19"/>
       <c r="E35" s="19">
@@ -5658,13 +5658,13 @@
     </row>
     <row r="36" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A36" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B36" s="19">
         <v>9</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D36" s="19"/>
       <c r="E36" s="19">
@@ -5783,13 +5783,13 @@
     </row>
     <row r="37" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A37" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B37" s="19">
         <v>10</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D37" s="19"/>
       <c r="E37" s="19">
@@ -5907,8 +5907,8 @@
       <c r="AR37" s="19"/>
     </row>
     <row r="38" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="59" t="s">
-        <v>157</v>
+      <c r="A38" s="54" t="s">
+        <v>156</v>
       </c>
       <c r="B38" s="55"/>
       <c r="C38" s="55"/>
@@ -5956,13 +5956,13 @@
     </row>
     <row r="39" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A39" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B39" s="19">
         <v>1</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D39" s="19"/>
       <c r="E39" s="19">
@@ -6036,7 +6036,7 @@
         <v>0.19928943749193886</v>
       </c>
       <c r="AB39" s="19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AC39" s="19">
         <v>891</v>
@@ -6072,24 +6072,24 @@
         <v>26</v>
       </c>
       <c r="AN39" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AO39" s="19"/>
       <c r="AP39" s="19"/>
       <c r="AQ39" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AR39" s="19"/>
     </row>
     <row r="40" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A40" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B40" s="19">
         <v>2</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D40" s="19"/>
       <c r="E40" s="19">
@@ -6163,7 +6163,7 @@
         <v>0.30625124412319887</v>
       </c>
       <c r="AB40" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AC40" s="19">
         <v>1212</v>
@@ -6199,24 +6199,24 @@
         <v>26</v>
       </c>
       <c r="AN40" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO40" s="19"/>
       <c r="AP40" s="19"/>
       <c r="AQ40" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AR40" s="19"/>
     </row>
     <row r="41" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A41" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B41" s="19">
         <v>3</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D41" s="19"/>
       <c r="E41" s="19">
@@ -6290,7 +6290,7 @@
         <v>0.18183140653602295</v>
       </c>
       <c r="AB41" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AC41" s="19">
         <v>1273</v>
@@ -6326,24 +6326,24 @@
         <v>26</v>
       </c>
       <c r="AN41" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO41" s="19"/>
       <c r="AP41" s="19"/>
       <c r="AQ41" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AR41" s="19"/>
     </row>
     <row r="42" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A42" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B42" s="19">
         <v>4</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D42" s="19"/>
       <c r="E42" s="19">
@@ -6417,7 +6417,7 @@
         <v>7.6820355900817455E-2</v>
       </c>
       <c r="AB42" s="19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AC42" s="19">
         <v>1221</v>
@@ -6449,24 +6449,24 @@
         <v>25</v>
       </c>
       <c r="AN42" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO42" s="19"/>
       <c r="AP42" s="19"/>
       <c r="AQ42" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AR42" s="19"/>
     </row>
     <row r="43" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A43" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B43" s="19">
         <v>5</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D43" s="19"/>
       <c r="E43" s="19">
@@ -6540,7 +6540,7 @@
         <v>7.0497969971101665E-2</v>
       </c>
       <c r="AB43" s="19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AC43" s="19">
         <v>1096</v>
@@ -6572,24 +6572,24 @@
         <v>27</v>
       </c>
       <c r="AN43" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO43" s="19"/>
       <c r="AP43" s="19"/>
       <c r="AQ43" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AR43" s="19"/>
     </row>
     <row r="44" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A44" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B44" s="19">
         <v>6</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D44" s="19"/>
       <c r="E44" s="19">
@@ -6663,7 +6663,7 @@
         <v>0.12776191125177114</v>
       </c>
       <c r="AB44" s="19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AC44" s="19">
         <v>687</v>
@@ -6691,24 +6691,24 @@
         <v>27</v>
       </c>
       <c r="AN44" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO44" s="19"/>
       <c r="AP44" s="19"/>
       <c r="AQ44" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AR44" s="19"/>
     </row>
     <row r="45" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A45" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B45" s="19">
         <v>7</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D45" s="19"/>
       <c r="E45" s="19">
@@ -6782,7 +6782,7 @@
         <v>0.17046470218564139</v>
       </c>
       <c r="AB45" s="19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AC45" s="19">
         <v>428</v>
@@ -6808,24 +6808,24 @@
         <v>27</v>
       </c>
       <c r="AN45" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO45" s="19"/>
       <c r="AP45" s="19"/>
       <c r="AQ45" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AR45" s="19"/>
     </row>
     <row r="46" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A46" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B46" s="19">
         <v>8</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D46" s="19"/>
       <c r="E46" s="19">
@@ -6899,7 +6899,7 @@
         <v>0.53596673617380275</v>
       </c>
       <c r="AB46" s="19" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AC46" s="19">
         <v>307</v>
@@ -6925,24 +6925,24 @@
         <v>27</v>
       </c>
       <c r="AN46" s="19" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AO46" s="19"/>
       <c r="AP46" s="19"/>
       <c r="AQ46" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AR46" s="19"/>
     </row>
     <row r="47" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A47" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B47" s="19">
         <v>9</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D47" s="19"/>
       <c r="E47" s="19">
@@ -7016,7 +7016,7 @@
         <v>0.1399456645816711</v>
       </c>
       <c r="AB47" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AC47" s="19">
         <v>244</v>
@@ -7042,24 +7042,24 @@
         <v>27</v>
       </c>
       <c r="AN47" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AO47" s="19"/>
       <c r="AP47" s="19"/>
       <c r="AQ47" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AR47" s="19"/>
     </row>
     <row r="48" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A48" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B48" s="19">
         <v>10</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D48" s="19"/>
       <c r="E48" s="19">
@@ -7133,7 +7133,7 @@
         <v>0.81329027425769451</v>
       </c>
       <c r="AB48" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AC48" s="19">
         <v>183</v>
@@ -7159,17 +7159,22 @@
         <v>27</v>
       </c>
       <c r="AN48" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AO48" s="19"/>
       <c r="AP48" s="19"/>
       <c r="AQ48" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AR48" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:AR1"/>
+    <mergeCell ref="A27:AR27"/>
+    <mergeCell ref="N2:Q2"/>
+    <mergeCell ref="A4:AR4"/>
+    <mergeCell ref="A15:AR15"/>
     <mergeCell ref="A38:AR38"/>
     <mergeCell ref="AQ2:AR2"/>
     <mergeCell ref="R2:Z2"/>
@@ -7177,11 +7182,6 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:M2"/>
     <mergeCell ref="AM2:AP2"/>
-    <mergeCell ref="A1:AR1"/>
-    <mergeCell ref="A27:AR27"/>
-    <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="A4:AR4"/>
-    <mergeCell ref="A15:AR15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7204,8 +7204,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="58" t="s">
-        <v>65</v>
+      <c r="A1" s="57" t="s">
+        <v>64</v>
       </c>
       <c r="B1" s="55"/>
       <c r="C1" s="55"/>
@@ -7252,7 +7252,7 @@
       <c r="AR1" s="55"/>
     </row>
     <row r="2" spans="1:44" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="56" t="s">
         <v>27</v>
       </c>
       <c r="B2" s="55"/>
@@ -7262,21 +7262,21 @@
       <c r="F2" s="55"/>
       <c r="G2" s="55"/>
       <c r="H2" s="55"/>
-      <c r="I2" s="57" t="s">
-        <v>127</v>
+      <c r="I2" s="56" t="s">
+        <v>126</v>
       </c>
       <c r="J2" s="55"/>
       <c r="K2" s="55"/>
       <c r="L2" s="55"/>
       <c r="M2" s="55"/>
-      <c r="N2" s="57" t="s">
-        <v>128</v>
+      <c r="N2" s="56" t="s">
+        <v>127</v>
       </c>
       <c r="O2" s="55"/>
       <c r="P2" s="55"/>
       <c r="Q2" s="55"/>
-      <c r="R2" s="57" t="s">
-        <v>129</v>
+      <c r="R2" s="56" t="s">
+        <v>128</v>
       </c>
       <c r="S2" s="55"/>
       <c r="T2" s="55"/>
@@ -7286,8 +7286,8 @@
       <c r="X2" s="55"/>
       <c r="Y2" s="55"/>
       <c r="Z2" s="55"/>
-      <c r="AA2" s="57" t="s">
-        <v>130</v>
+      <c r="AA2" s="56" t="s">
+        <v>129</v>
       </c>
       <c r="AB2" s="55"/>
       <c r="AC2" s="55"/>
@@ -7300,32 +7300,32 @@
       <c r="AJ2" s="55"/>
       <c r="AK2" s="55"/>
       <c r="AL2" s="55"/>
-      <c r="AM2" s="57" t="s">
-        <v>131</v>
+      <c r="AM2" s="56" t="s">
+        <v>130</v>
       </c>
       <c r="AN2" s="55"/>
       <c r="AO2" s="55"/>
       <c r="AP2" s="55"/>
-      <c r="AQ2" s="57" t="s">
-        <v>132</v>
+      <c r="AQ2" s="56" t="s">
+        <v>131</v>
       </c>
       <c r="AR2" s="55"/>
     </row>
     <row r="3" spans="1:44" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>133</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>134</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>28</v>
       </c>
       <c r="D3" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>135</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>136</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>29</v>
@@ -7334,7 +7334,7 @@
         <v>30</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>31</v>
@@ -7346,16 +7346,16 @@
         <v>33</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M3" s="13" t="s">
         <v>6</v>
       </c>
       <c r="N3" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="O3" s="14" t="s">
         <v>139</v>
-      </c>
-      <c r="O3" s="14" t="s">
-        <v>140</v>
       </c>
       <c r="P3" s="14" t="s">
         <v>3</v>
@@ -7379,7 +7379,7 @@
         <v>38</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="X3" s="15" t="s">
         <v>5</v>
@@ -7388,66 +7388,66 @@
         <v>39</v>
       </c>
       <c r="Z3" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA3" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="AB3" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="AA3" s="16" t="s">
+      <c r="AC3" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="AB3" s="16" t="s">
+      <c r="AD3" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE3" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF3" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG3" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH3" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI3" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="AJ3" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="AK3" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL3" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM3" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN3" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="AC3" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD3" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE3" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF3" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG3" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH3" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI3" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="AJ3" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK3" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="AL3" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AM3" s="17" t="s">
+      <c r="AO3" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="AP3" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="AQ3" s="18" t="s">
         <v>51</v>
-      </c>
-      <c r="AN3" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="AO3" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="AP3" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="AQ3" s="18" t="s">
-        <v>52</v>
       </c>
       <c r="AR3" s="18" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="59" t="s">
-        <v>166</v>
+      <c r="A4" s="54" t="s">
+        <v>165</v>
       </c>
       <c r="B4" s="55"/>
       <c r="C4" s="55"/>
@@ -7495,13 +7495,13 @@
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B5" s="19">
         <v>1</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D5" s="19">
         <v>3</v>
@@ -7577,7 +7577,7 @@
         <v>0.24904076328012636</v>
       </c>
       <c r="AB5" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AC5" s="19">
         <v>650</v>
@@ -7609,7 +7609,7 @@
         <v>24</v>
       </c>
       <c r="AN5" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO5" s="19">
         <v>0</v>
@@ -7620,13 +7620,13 @@
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B6" s="19">
         <v>2</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6" s="19">
         <v>3</v>
@@ -7702,7 +7702,7 @@
         <v>0.11728272205060758</v>
       </c>
       <c r="AB6" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC6" s="19">
         <v>1268</v>
@@ -7732,7 +7732,7 @@
         <v>25</v>
       </c>
       <c r="AN6" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO6" s="19">
         <v>0</v>
@@ -7743,13 +7743,13 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B7" s="19">
         <v>3</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D7" s="19">
         <v>3</v>
@@ -7825,7 +7825,7 @@
         <v>0.12821282508516391</v>
       </c>
       <c r="AB7" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC7" s="19">
         <v>1539</v>
@@ -7861,7 +7861,7 @@
         <v>26</v>
       </c>
       <c r="AN7" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO7" s="19">
         <v>0</v>
@@ -7872,13 +7872,13 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B8" s="19">
         <v>4</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D8" s="19">
         <v>3</v>
@@ -7954,7 +7954,7 @@
         <v>0.18284422404646647</v>
       </c>
       <c r="AB8" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC8" s="19">
         <v>1708</v>
@@ -7990,28 +7990,28 @@
         <v>29</v>
       </c>
       <c r="AN8" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO8" s="19">
         <v>1</v>
       </c>
       <c r="AP8" s="19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AQ8" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AR8" s="19"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B9" s="19">
         <v>5</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D9" s="19">
         <v>3</v>
@@ -8087,7 +8087,7 @@
         <v>0.1810196386787471</v>
       </c>
       <c r="AB9" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC9" s="19">
         <v>2242</v>
@@ -8123,7 +8123,7 @@
         <v>34</v>
       </c>
       <c r="AN9" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AO9" s="19">
         <v>1</v>
@@ -8134,13 +8134,13 @@
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B10" s="19">
         <v>6</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10" s="19">
         <v>3</v>
@@ -8218,7 +8218,7 @@
         <v>0.18826667399787078</v>
       </c>
       <c r="AB10" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AC10" s="19">
         <v>2961</v>
@@ -8254,7 +8254,7 @@
         <v>50</v>
       </c>
       <c r="AN10" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AO10" s="19">
         <v>1</v>
@@ -8262,18 +8262,18 @@
       <c r="AP10" s="19"/>
       <c r="AQ10" s="19"/>
       <c r="AR10" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B11" s="19">
         <v>7</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D11" s="19">
         <v>3</v>
@@ -8351,7 +8351,7 @@
         <v>0.20006201808247814</v>
       </c>
       <c r="AB11" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AC11" s="19">
         <v>3158</v>
@@ -8387,7 +8387,7 @@
         <v>51</v>
       </c>
       <c r="AN11" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO11" s="19">
         <v>1</v>
@@ -8398,13 +8398,13 @@
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B12" s="19">
         <v>8</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" s="19">
         <v>3</v>
@@ -8482,7 +8482,7 @@
         <v>0.30830999205616344</v>
       </c>
       <c r="AB12" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AC12" s="19">
         <v>3559</v>
@@ -8518,22 +8518,22 @@
         <v>69</v>
       </c>
       <c r="AN12" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO12" s="19">
         <v>1</v>
       </c>
       <c r="AP12" s="19"/>
       <c r="AQ12" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AR12" s="19" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="13" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="59" t="s">
         <v>173</v>
-      </c>
-    </row>
-    <row r="13" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="61" t="s">
-        <v>174</v>
       </c>
       <c r="B13" s="55"/>
       <c r="C13" s="55"/>
@@ -8581,13 +8581,13 @@
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B14" s="19">
         <v>1</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D14" s="19">
         <v>3</v>
@@ -8665,7 +8665,7 @@
         <v>2.483269928717537</v>
       </c>
       <c r="AB14" s="19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AC14" s="19">
         <v>67</v>
@@ -8701,26 +8701,26 @@
         <v>24</v>
       </c>
       <c r="AN14" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO14" s="19">
         <v>0</v>
       </c>
       <c r="AP14" s="19"/>
       <c r="AQ14" s="19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AR14" s="19"/>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B15" s="19">
         <v>2</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D15" s="19">
         <v>3</v>
@@ -8832,7 +8832,7 @@
         <v>24</v>
       </c>
       <c r="AN15" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO15" s="19">
         <v>0</v>
@@ -8843,13 +8843,13 @@
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B16" s="19">
         <v>3</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D16" s="19">
         <v>3</v>
@@ -8961,7 +8961,7 @@
         <v>24</v>
       </c>
       <c r="AN16" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO16" s="19">
         <v>0</v>
@@ -8972,13 +8972,13 @@
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B17" s="19">
         <v>4</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" s="19">
         <v>3</v>
@@ -9090,7 +9090,7 @@
         <v>25</v>
       </c>
       <c r="AN17" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO17" s="19">
         <v>0</v>
@@ -9101,13 +9101,13 @@
     </row>
     <row r="18" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B18" s="19">
         <v>5</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D18" s="19">
         <v>3</v>
@@ -9219,7 +9219,7 @@
         <v>25</v>
       </c>
       <c r="AN18" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO18" s="19">
         <v>0</v>
@@ -9230,13 +9230,13 @@
     </row>
     <row r="19" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B19" s="19">
         <v>6</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D19" s="19">
         <v>3</v>
@@ -9333,13 +9333,13 @@
     </row>
     <row r="20" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B20" s="19">
         <v>7</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D20" s="19">
         <v>3</v>
@@ -9436,13 +9436,13 @@
     </row>
     <row r="21" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B21" s="19">
         <v>8</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D21" s="19">
         <v>3</v>
@@ -9538,8 +9538,8 @@
       <c r="AR21" s="19"/>
     </row>
     <row r="22" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="59" t="s">
-        <v>176</v>
+      <c r="A22" s="54" t="s">
+        <v>175</v>
       </c>
       <c r="B22" s="55"/>
       <c r="C22" s="55"/>
@@ -9587,13 +9587,13 @@
     </row>
     <row r="23" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B23" s="19">
         <v>1</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D23" s="19">
         <v>3</v>
@@ -9669,7 +9669,7 @@
         <v>0.18427253168506441</v>
       </c>
       <c r="AB23" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AC23" s="19">
         <v>606</v>
@@ -9695,7 +9695,7 @@
         <v>24</v>
       </c>
       <c r="AN23" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO23" s="19">
         <v>0</v>
@@ -9706,13 +9706,13 @@
     </row>
     <row r="24" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B24" s="19">
         <v>2</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D24" s="19">
         <v>3</v>
@@ -9788,7 +9788,7 @@
         <v>9.715450033821478E-2</v>
       </c>
       <c r="AB24" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC24" s="19">
         <v>1142</v>
@@ -9816,7 +9816,7 @@
         <v>24</v>
       </c>
       <c r="AN24" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO24" s="19">
         <v>0</v>
@@ -9827,13 +9827,13 @@
     </row>
     <row r="25" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B25" s="19">
         <v>3</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D25" s="19">
         <v>3</v>
@@ -9909,7 +9909,7 @@
         <v>8.3583543485279244E-2</v>
       </c>
       <c r="AB25" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC25" s="19">
         <v>1378</v>
@@ -9939,7 +9939,7 @@
         <v>25</v>
       </c>
       <c r="AN25" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO25" s="19">
         <v>0</v>
@@ -9950,13 +9950,13 @@
     </row>
     <row r="26" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B26" s="19">
         <v>4</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D26" s="19">
         <v>3</v>
@@ -10032,7 +10032,7 @@
         <v>8.400811866939982E-2</v>
       </c>
       <c r="AB26" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC26" s="19">
         <v>1432</v>
@@ -10066,26 +10066,26 @@
         <v>26</v>
       </c>
       <c r="AN26" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO26" s="19">
         <v>1</v>
       </c>
       <c r="AP26" s="19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AQ26" s="19"/>
       <c r="AR26" s="19"/>
     </row>
     <row r="27" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B27" s="19">
         <v>5</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D27" s="19">
         <v>3</v>
@@ -10161,7 +10161,7 @@
         <v>8.3921379232951496E-2</v>
       </c>
       <c r="AB27" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC27" s="19">
         <v>1461</v>
@@ -10195,28 +10195,28 @@
         <v>27</v>
       </c>
       <c r="AN27" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO27" s="19">
         <v>1</v>
       </c>
       <c r="AP27" s="19"/>
       <c r="AQ27" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AR27" s="19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="28" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B28" s="19">
         <v>6</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D28" s="19">
         <v>3</v>
@@ -10292,7 +10292,7 @@
         <v>4.7736470463591869E-2</v>
       </c>
       <c r="AB28" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC28" s="19">
         <v>1409</v>
@@ -10318,7 +10318,7 @@
         <v>29</v>
       </c>
       <c r="AN28" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO28" s="19">
         <v>1</v>
@@ -10329,13 +10329,13 @@
     </row>
     <row r="29" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A29" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B29" s="19">
         <v>7</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D29" s="19">
         <v>3</v>
@@ -10411,7 +10411,7 @@
         <v>4.9250932443815558E-2</v>
       </c>
       <c r="AB29" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC29" s="19">
         <v>1465</v>
@@ -10435,7 +10435,7 @@
         <v>38</v>
       </c>
       <c r="AN29" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO29" s="19">
         <v>1</v>
@@ -10446,13 +10446,13 @@
     </row>
     <row r="30" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A30" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B30" s="19">
         <v>8</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D30" s="19">
         <v>3</v>
@@ -10528,7 +10528,7 @@
         <v>0.21031413897575299</v>
       </c>
       <c r="AB30" s="19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AC30" s="19">
         <v>3011</v>
@@ -10564,26 +10564,26 @@
         <v>107</v>
       </c>
       <c r="AN30" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO30" s="19">
         <v>1</v>
       </c>
       <c r="AP30" s="19"/>
       <c r="AQ30" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AR30" s="19"/>
     </row>
     <row r="31" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A31" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B31" s="19">
         <v>9</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D31" s="19">
         <v>3</v>
@@ -10661,12 +10661,12 @@
       <c r="AP31" s="19"/>
       <c r="AQ31" s="19"/>
       <c r="AR31" s="19" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="54" t="s">
         <v>179</v>
-      </c>
-    </row>
-    <row r="32" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="59" t="s">
-        <v>180</v>
       </c>
       <c r="B32" s="55"/>
       <c r="C32" s="55"/>
@@ -10714,13 +10714,13 @@
     </row>
     <row r="33" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A33" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B33" s="19">
         <v>1</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D33" s="19">
         <v>3</v>
@@ -10798,7 +10798,7 @@
         <v>0.19741735191348231</v>
       </c>
       <c r="AB33" s="19" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC33" s="19">
         <v>383</v>
@@ -10822,7 +10822,7 @@
         <v>24</v>
       </c>
       <c r="AN33" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO33" s="19">
         <v>0</v>
@@ -10833,13 +10833,13 @@
     </row>
     <row r="34" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A34" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B34" s="19">
         <v>2</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D34" s="19">
         <v>3</v>
@@ -10917,7 +10917,7 @@
         <v>0.25062564599759102</v>
       </c>
       <c r="AB34" s="19" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC34" s="19">
         <v>514</v>
@@ -10945,7 +10945,7 @@
         <v>25</v>
       </c>
       <c r="AN34" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO34" s="19">
         <v>0</v>
@@ -10956,13 +10956,13 @@
     </row>
     <row r="35" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A35" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B35" s="19">
         <v>3</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D35" s="19">
         <v>3</v>
@@ -11040,7 +11040,7 @@
         <v>0.19399254228072299</v>
       </c>
       <c r="AB35" s="19" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC35" s="19">
         <v>698</v>
@@ -11068,7 +11068,7 @@
         <v>29</v>
       </c>
       <c r="AN35" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO35" s="19">
         <v>0</v>
@@ -11079,13 +11079,13 @@
     </row>
     <row r="36" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A36" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B36" s="19">
         <v>4</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D36" s="19">
         <v>3</v>
@@ -11163,7 +11163,7 @@
         <v>0.21463745615387531</v>
       </c>
       <c r="AB36" s="19" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC36" s="19">
         <v>1173</v>
@@ -11197,30 +11197,30 @@
         <v>37</v>
       </c>
       <c r="AN36" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AO36" s="19">
         <v>1</v>
       </c>
       <c r="AP36" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="AQ36" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="AR36" s="19" t="s">
         <v>182</v>
-      </c>
-      <c r="AQ36" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="AR36" s="19" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="37" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A37" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B37" s="19">
         <v>5</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D37" s="19">
         <v>3</v>
@@ -11298,7 +11298,7 @@
         <v>0.20555895062524801</v>
       </c>
       <c r="AB37" s="19" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AC37" s="19">
         <v>1891</v>
@@ -11334,28 +11334,28 @@
         <v>60</v>
       </c>
       <c r="AN37" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AO37" s="19">
         <v>1</v>
       </c>
       <c r="AP37" s="19"/>
       <c r="AQ37" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AR37" s="19" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="38" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A38" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B38" s="19">
         <v>6</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D38" s="19">
         <v>3</v>
@@ -11433,12 +11433,12 @@
       <c r="AP38" s="19"/>
       <c r="AQ38" s="19"/>
       <c r="AR38" s="19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="39" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="59" t="s">
-        <v>185</v>
+      <c r="A39" s="54" t="s">
+        <v>184</v>
       </c>
       <c r="B39" s="55"/>
       <c r="C39" s="55"/>
@@ -11486,13 +11486,13 @@
     </row>
     <row r="40" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A40" s="19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B40" s="19">
         <v>1</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D40" s="19">
         <v>3</v>
@@ -11570,7 +11570,7 @@
         <v>0.39544102936728032</v>
       </c>
       <c r="AB40" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AC40" s="19">
         <v>203</v>
@@ -11594,7 +11594,7 @@
         <v>29</v>
       </c>
       <c r="AN40" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO40" s="19">
         <v>0</v>
@@ -11605,13 +11605,13 @@
     </row>
     <row r="41" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A41" s="19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B41" s="19">
         <v>2</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D41" s="19">
         <v>3</v>
@@ -11689,7 +11689,7 @@
         <v>0.31432703704091836</v>
       </c>
       <c r="AB41" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AC41" s="19">
         <v>263</v>
@@ -11713,26 +11713,26 @@
         <v>29</v>
       </c>
       <c r="AN41" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO41" s="19">
         <v>0</v>
       </c>
       <c r="AP41" s="19"/>
       <c r="AQ41" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AR41" s="19"/>
     </row>
     <row r="42" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A42" s="19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B42" s="19">
         <v>3</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D42" s="19">
         <v>3</v>
@@ -11810,7 +11810,7 @@
         <v>0.23638180703186989</v>
       </c>
       <c r="AB42" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AC42" s="19">
         <v>368</v>
@@ -11838,7 +11838,7 @@
         <v>34</v>
       </c>
       <c r="AN42" s="19" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO42" s="19">
         <v>0</v>
@@ -11849,13 +11849,13 @@
     </row>
     <row r="43" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A43" s="19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B43" s="19">
         <v>4</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D43" s="19">
         <v>3</v>
@@ -11933,7 +11933,7 @@
         <v>0.15864308017100967</v>
       </c>
       <c r="AB43" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AC43" s="19">
         <v>675</v>
@@ -11961,7 +11961,7 @@
         <v>47</v>
       </c>
       <c r="AN43" s="19" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO43" s="19">
         <v>0</v>
@@ -11972,13 +11972,13 @@
     </row>
     <row r="44" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A44" s="19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B44" s="19">
         <v>5</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D44" s="19">
         <v>3</v>
@@ -12056,7 +12056,7 @@
         <v>0.11517929758169376</v>
       </c>
       <c r="AB44" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AC44" s="19">
         <v>1288</v>
@@ -12088,20 +12088,20 @@
         <v>80</v>
       </c>
       <c r="AN44" s="19" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AO44" s="19">
         <v>1</v>
       </c>
       <c r="AP44" s="19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AQ44" s="19"/>
       <c r="AR44" s="19"/>
     </row>
     <row r="45" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="54" t="s">
-        <v>188</v>
+      <c r="A45" s="58" t="s">
+        <v>187</v>
       </c>
       <c r="B45" s="55"/>
       <c r="C45" s="55"/>
@@ -12149,13 +12149,13 @@
     </row>
     <row r="46" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A46" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B46" s="19">
         <v>1</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D46" s="19">
         <v>1</v>
@@ -12231,7 +12231,7 @@
         <v>0.47576611198093893</v>
       </c>
       <c r="AB46" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC46" s="19">
         <v>1070</v>
@@ -12267,7 +12267,7 @@
         <v>26</v>
       </c>
       <c r="AN46" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO46" s="19">
         <v>0</v>
@@ -12278,13 +12278,13 @@
     </row>
     <row r="47" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A47" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B47" s="19">
         <v>2</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D47" s="19">
         <v>1</v>
@@ -12360,7 +12360,7 @@
         <v>0.43540738479622992</v>
       </c>
       <c r="AB47" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC47" s="19">
         <v>1174</v>
@@ -12396,7 +12396,7 @@
         <v>27</v>
       </c>
       <c r="AN47" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO47" s="19">
         <v>0</v>
@@ -12407,13 +12407,13 @@
     </row>
     <row r="48" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A48" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B48" s="19">
         <v>3</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D48" s="19">
         <v>1</v>
@@ -12489,7 +12489,7 @@
         <v>0.41501886106899882</v>
       </c>
       <c r="AB48" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC48" s="19">
         <v>1232</v>
@@ -12525,7 +12525,7 @@
         <v>31</v>
       </c>
       <c r="AN48" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO48" s="19">
         <v>0</v>
@@ -12536,13 +12536,13 @@
     </row>
     <row r="49" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A49" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B49" s="19">
         <v>4</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D49" s="19">
         <v>1</v>
@@ -12618,7 +12618,7 @@
         <v>0.37979209284577076</v>
       </c>
       <c r="AB49" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC49" s="19">
         <v>1343</v>
@@ -12654,7 +12654,7 @@
         <v>37</v>
       </c>
       <c r="AN49" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO49" s="19">
         <v>0</v>
@@ -12665,13 +12665,13 @@
     </row>
     <row r="50" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A50" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B50" s="19">
         <v>5</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D50" s="19">
         <v>1</v>
@@ -12754,13 +12754,13 @@
     </row>
     <row r="51" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A51" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B51" s="19">
         <v>6</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D51" s="19">
         <v>1</v>
@@ -12841,13 +12841,13 @@
     </row>
     <row r="52" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A52" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B52" s="19">
         <v>7</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D52" s="19">
         <v>1</v>
@@ -12928,13 +12928,13 @@
     </row>
     <row r="53" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A53" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B53" s="19">
         <v>8</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D53" s="19">
         <v>1</v>
@@ -13014,8 +13014,8 @@
       <c r="AR53" s="19"/>
     </row>
     <row r="54" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="54" t="s">
-        <v>190</v>
+      <c r="A54" s="58" t="s">
+        <v>189</v>
       </c>
       <c r="B54" s="55"/>
       <c r="C54" s="55"/>
@@ -13063,13 +13063,13 @@
     </row>
     <row r="55" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A55" s="19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B55" s="19">
         <v>1</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D55" s="19">
         <v>1</v>
@@ -13150,13 +13150,13 @@
     </row>
     <row r="56" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A56" s="19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B56" s="19">
         <v>2</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D56" s="19">
         <v>1</v>
@@ -13237,13 +13237,13 @@
     </row>
     <row r="57" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A57" s="19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B57" s="19">
         <v>3</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D57" s="19">
         <v>1</v>
@@ -13324,13 +13324,13 @@
     </row>
     <row r="58" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A58" s="19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B58" s="19">
         <v>4</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D58" s="19">
         <v>1</v>
@@ -13411,13 +13411,13 @@
     </row>
     <row r="59" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A59" s="19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B59" s="19">
         <v>5</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D59" s="19">
         <v>1</v>
@@ -13498,13 +13498,13 @@
     </row>
     <row r="60" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A60" s="19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B60" s="19">
         <v>6</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D60" s="19">
         <v>1</v>
@@ -13585,13 +13585,13 @@
     </row>
     <row r="61" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A61" s="19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B61" s="19">
         <v>7</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D61" s="19">
         <v>1</v>
@@ -13672,13 +13672,13 @@
     </row>
     <row r="62" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A62" s="19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B62" s="19">
         <v>8</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D62" s="19">
         <v>1</v>
@@ -13758,8 +13758,8 @@
       <c r="AR62" s="19"/>
     </row>
     <row r="63" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="54" t="s">
-        <v>192</v>
+      <c r="A63" s="58" t="s">
+        <v>191</v>
       </c>
       <c r="B63" s="55"/>
       <c r="C63" s="55"/>
@@ -13807,13 +13807,13 @@
     </row>
     <row r="64" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A64" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B64" s="19">
         <v>1</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D64" s="19">
         <v>1</v>
@@ -13892,13 +13892,13 @@
     </row>
     <row r="65" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A65" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B65" s="19">
         <v>2</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D65" s="19">
         <v>1</v>
@@ -13977,13 +13977,13 @@
     </row>
     <row r="66" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A66" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B66" s="19">
         <v>3</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D66" s="19">
         <v>1</v>
@@ -14062,13 +14062,13 @@
     </row>
     <row r="67" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A67" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B67" s="19">
         <v>4</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D67" s="19">
         <v>1</v>
@@ -14147,13 +14147,13 @@
     </row>
     <row r="68" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A68" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B68" s="19">
         <v>5</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D68" s="19">
         <v>1</v>
@@ -14232,13 +14232,13 @@
     </row>
     <row r="69" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A69" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B69" s="19">
         <v>6</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D69" s="19">
         <v>1</v>
@@ -14317,13 +14317,13 @@
     </row>
     <row r="70" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A70" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B70" s="19">
         <v>7</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D70" s="19">
         <v>1</v>
@@ -14402,13 +14402,13 @@
     </row>
     <row r="71" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A71" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B71" s="19">
         <v>8</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D71" s="19">
         <v>1</v>
@@ -14487,13 +14487,13 @@
     </row>
     <row r="72" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A72" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B72" s="19">
         <v>9</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D72" s="19">
         <v>1</v>
@@ -14572,13 +14572,13 @@
     </row>
     <row r="73" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A73" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B73" s="19">
         <v>10</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D73" s="19">
         <v>1</v>
@@ -14657,13 +14657,13 @@
     </row>
     <row r="74" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A74" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B74" s="19">
         <v>11</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D74" s="19">
         <v>1</v>
@@ -14742,13 +14742,13 @@
     </row>
     <row r="75" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A75" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B75" s="19">
         <v>12</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D75" s="19">
         <v>1</v>
@@ -14827,6 +14827,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:AR1"/>
+    <mergeCell ref="A45:AR45"/>
+    <mergeCell ref="N2:Q2"/>
+    <mergeCell ref="A22:AR22"/>
+    <mergeCell ref="A4:AR4"/>
+    <mergeCell ref="A39:AR39"/>
     <mergeCell ref="A54:AR54"/>
     <mergeCell ref="A63:AR63"/>
     <mergeCell ref="AQ2:AR2"/>
@@ -14837,12 +14843,6 @@
     <mergeCell ref="A13:AR13"/>
     <mergeCell ref="I2:M2"/>
     <mergeCell ref="AM2:AP2"/>
-    <mergeCell ref="A1:AR1"/>
-    <mergeCell ref="A45:AR45"/>
-    <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="A22:AR22"/>
-    <mergeCell ref="A4:AR4"/>
-    <mergeCell ref="A39:AR39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14865,8 +14865,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="58" t="s">
-        <v>76</v>
+      <c r="A1" s="57" t="s">
+        <v>75</v>
       </c>
       <c r="B1" s="55"/>
       <c r="C1" s="55"/>
@@ -14913,7 +14913,7 @@
       <c r="AR1" s="55"/>
     </row>
     <row r="2" spans="1:44" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="56" t="s">
         <v>27</v>
       </c>
       <c r="B2" s="55"/>
@@ -14923,21 +14923,21 @@
       <c r="F2" s="55"/>
       <c r="G2" s="55"/>
       <c r="H2" s="55"/>
-      <c r="I2" s="57" t="s">
-        <v>127</v>
+      <c r="I2" s="56" t="s">
+        <v>126</v>
       </c>
       <c r="J2" s="55"/>
       <c r="K2" s="55"/>
       <c r="L2" s="55"/>
       <c r="M2" s="55"/>
-      <c r="N2" s="57" t="s">
-        <v>128</v>
+      <c r="N2" s="56" t="s">
+        <v>127</v>
       </c>
       <c r="O2" s="55"/>
       <c r="P2" s="55"/>
       <c r="Q2" s="55"/>
-      <c r="R2" s="57" t="s">
-        <v>129</v>
+      <c r="R2" s="56" t="s">
+        <v>128</v>
       </c>
       <c r="S2" s="55"/>
       <c r="T2" s="55"/>
@@ -14947,8 +14947,8 @@
       <c r="X2" s="55"/>
       <c r="Y2" s="55"/>
       <c r="Z2" s="55"/>
-      <c r="AA2" s="57" t="s">
-        <v>130</v>
+      <c r="AA2" s="56" t="s">
+        <v>129</v>
       </c>
       <c r="AB2" s="55"/>
       <c r="AC2" s="55"/>
@@ -14961,32 +14961,32 @@
       <c r="AJ2" s="55"/>
       <c r="AK2" s="55"/>
       <c r="AL2" s="55"/>
-      <c r="AM2" s="57" t="s">
-        <v>131</v>
+      <c r="AM2" s="56" t="s">
+        <v>130</v>
       </c>
       <c r="AN2" s="55"/>
       <c r="AO2" s="55"/>
       <c r="AP2" s="55"/>
-      <c r="AQ2" s="57" t="s">
-        <v>132</v>
+      <c r="AQ2" s="56" t="s">
+        <v>131</v>
       </c>
       <c r="AR2" s="55"/>
     </row>
     <row r="3" spans="1:44" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>133</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>134</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>28</v>
       </c>
       <c r="D3" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>135</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>136</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>29</v>
@@ -14995,7 +14995,7 @@
         <v>30</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>31</v>
@@ -15007,16 +15007,16 @@
         <v>33</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M3" s="13" t="s">
         <v>6</v>
       </c>
       <c r="N3" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="O3" s="14" t="s">
         <v>139</v>
-      </c>
-      <c r="O3" s="14" t="s">
-        <v>140</v>
       </c>
       <c r="P3" s="14" t="s">
         <v>3</v>
@@ -15040,7 +15040,7 @@
         <v>38</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="X3" s="15" t="s">
         <v>5</v>
@@ -15049,66 +15049,66 @@
         <v>39</v>
       </c>
       <c r="Z3" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA3" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="AB3" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="AA3" s="16" t="s">
+      <c r="AC3" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="AB3" s="16" t="s">
+      <c r="AD3" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE3" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF3" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG3" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH3" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI3" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="AJ3" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="AK3" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL3" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM3" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN3" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="AC3" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD3" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE3" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF3" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG3" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH3" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI3" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="AJ3" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK3" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="AL3" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AM3" s="17" t="s">
+      <c r="AO3" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="AP3" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="AQ3" s="18" t="s">
         <v>51</v>
-      </c>
-      <c r="AN3" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="AO3" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="AP3" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="AQ3" s="18" t="s">
-        <v>52</v>
       </c>
       <c r="AR3" s="18" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="59" t="s">
-        <v>194</v>
+      <c r="A4" s="54" t="s">
+        <v>193</v>
       </c>
       <c r="B4" s="55"/>
       <c r="C4" s="55"/>
@@ -15156,13 +15156,13 @@
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B5" s="19">
         <v>1</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D5" s="19">
         <v>3</v>
@@ -15238,7 +15238,7 @@
         <v>0.24387599135977522</v>
       </c>
       <c r="AB5" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC5" s="19">
         <v>648</v>
@@ -15266,30 +15266,30 @@
         <v>27</v>
       </c>
       <c r="AN5" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO5" s="19">
         <v>0</v>
       </c>
       <c r="AP5" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ5" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AR5" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B6" s="19">
         <v>2</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6" s="19">
         <v>3</v>
@@ -15365,7 +15365,7 @@
         <v>0.13378549835581022</v>
       </c>
       <c r="AB6" s="19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AC6" s="19">
         <v>1024</v>
@@ -15393,30 +15393,30 @@
         <v>26</v>
       </c>
       <c r="AN6" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO6" s="19">
         <v>0</v>
       </c>
       <c r="AP6" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ6" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AR6" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B7" s="19">
         <v>3</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D7" s="19">
         <v>3</v>
@@ -15492,7 +15492,7 @@
         <v>0.23874306425289715</v>
       </c>
       <c r="AB7" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AC7" s="19">
         <v>1225</v>
@@ -15524,30 +15524,30 @@
         <v>25</v>
       </c>
       <c r="AN7" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO7" s="19">
         <v>0</v>
       </c>
       <c r="AP7" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ7" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AR7" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B8" s="19">
         <v>4</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D8" s="19">
         <v>3</v>
@@ -15623,7 +15623,7 @@
         <v>0.25351286735749001</v>
       </c>
       <c r="AB8" s="19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AC8" s="19">
         <v>896</v>
@@ -15653,30 +15653,30 @@
         <v>27</v>
       </c>
       <c r="AN8" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO8" s="19">
         <v>0</v>
       </c>
       <c r="AP8" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ8" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AR8" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B9" s="19">
         <v>5</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D9" s="19">
         <v>3</v>
@@ -15752,7 +15752,7 @@
         <v>0.371243328008517</v>
       </c>
       <c r="AB9" s="19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AC9" s="19">
         <v>585</v>
@@ -15780,30 +15780,30 @@
         <v>27</v>
       </c>
       <c r="AN9" s="19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AO9" s="19">
         <v>0</v>
       </c>
       <c r="AP9" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ9" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AR9" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B10" s="19">
         <v>6</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10" s="19">
         <v>3</v>
@@ -15879,7 +15879,7 @@
         <v>0.66542075592364536</v>
       </c>
       <c r="AB10" s="19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AC10" s="19">
         <v>317</v>
@@ -15905,30 +15905,30 @@
         <v>27</v>
       </c>
       <c r="AN10" s="19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AO10" s="19">
         <v>0</v>
       </c>
       <c r="AP10" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ10" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AR10" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B11" s="19">
         <v>7</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D11" s="19">
         <v>3</v>
@@ -16004,7 +16004,7 @@
         <v>0.89101905157532157</v>
       </c>
       <c r="AB11" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AC11" s="19">
         <v>226</v>
@@ -16030,30 +16030,30 @@
         <v>27</v>
       </c>
       <c r="AN11" s="19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AO11" s="19">
         <v>0</v>
       </c>
       <c r="AP11" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ11" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AR11" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B12" s="19">
         <v>8</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" s="19">
         <v>3</v>
@@ -16129,7 +16129,7 @@
         <v>0.41410094401816416</v>
       </c>
       <c r="AB12" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AC12" s="19">
         <v>140</v>
@@ -16151,30 +16151,30 @@
         <v>27</v>
       </c>
       <c r="AN12" s="19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AO12" s="19">
         <v>0</v>
       </c>
       <c r="AP12" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ12" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AR12" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B13" s="19">
         <v>9</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" s="19">
         <v>3</v>
@@ -16250,7 +16250,7 @@
         <v>0.43602935092981787</v>
       </c>
       <c r="AB13" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AC13" s="19">
         <v>103</v>
@@ -16272,30 +16272,30 @@
         <v>27</v>
       </c>
       <c r="AN13" s="19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AO13" s="19">
         <v>0</v>
       </c>
       <c r="AP13" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ13" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AR13" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B14" s="19">
         <v>10</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" s="19">
         <v>3</v>
@@ -16371,7 +16371,7 @@
         <v>0.56211653952340557</v>
       </c>
       <c r="AB14" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AC14" s="19">
         <v>79</v>
@@ -16393,30 +16393,30 @@
         <v>27</v>
       </c>
       <c r="AN14" s="19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AO14" s="19">
         <v>0</v>
       </c>
       <c r="AP14" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ14" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AR14" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B15" s="19">
         <v>11</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" s="19">
         <v>3</v>
@@ -16492,7 +16492,7 @@
         <v>0.73992774735280409</v>
       </c>
       <c r="AB15" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AC15" s="19">
         <v>63</v>
@@ -16514,24 +16514,24 @@
         <v>27</v>
       </c>
       <c r="AN15" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="AO15" s="19">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="AQ15" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="AR15" s="19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="61" t="s">
         <v>197</v>
-      </c>
-      <c r="AO15" s="19">
-        <v>0</v>
-      </c>
-      <c r="AP15" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="AQ15" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="AR15" s="19" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="60" t="s">
-        <v>198</v>
       </c>
       <c r="B16" s="55"/>
       <c r="C16" s="55"/>
@@ -16550,7 +16550,7 @@
       <c r="P16" s="55"/>
       <c r="Q16" s="55"/>
       <c r="R16" s="55"/>
-      <c r="S16" s="56"/>
+      <c r="S16" s="60"/>
       <c r="T16" s="55"/>
       <c r="U16" s="55"/>
       <c r="V16" s="55"/>
@@ -16579,13 +16579,13 @@
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B17" s="19">
         <v>1</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D17" s="19">
         <v>3</v>
@@ -16661,7 +16661,7 @@
         <v>0.72884039405071399</v>
       </c>
       <c r="AB17" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AC17" s="19">
         <v>1250</v>
@@ -16697,30 +16697,30 @@
         <v>54</v>
       </c>
       <c r="AN17" s="19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AO17" s="19">
         <v>0</v>
       </c>
       <c r="AP17" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ17" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AR17" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B18" s="19">
         <v>2</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D18" s="19">
         <v>3</v>
@@ -16796,7 +16796,7 @@
         <v>0.17069924645276843</v>
       </c>
       <c r="AB18" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AC18" s="19">
         <v>1607</v>
@@ -16828,30 +16828,30 @@
         <v>40</v>
       </c>
       <c r="AN18" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO18" s="19">
         <v>0</v>
       </c>
       <c r="AP18" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ18" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AR18" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B19" s="19">
         <v>3</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D19" s="19">
         <v>3</v>
@@ -16929,7 +16929,7 @@
         <v>9.4861254798835087E-2</v>
       </c>
       <c r="AB19" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC19" s="19">
         <v>1856</v>
@@ -16965,30 +16965,30 @@
         <v>31</v>
       </c>
       <c r="AN19" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO19" s="19">
         <v>1</v>
       </c>
       <c r="AP19" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ19" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AR19" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B20" s="19">
         <v>4</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D20" s="19">
         <v>3</v>
@@ -17062,7 +17062,7 @@
         <v>0.14059293253147795</v>
       </c>
       <c r="AB20" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AC20" s="19">
         <v>1460</v>
@@ -17096,30 +17096,30 @@
         <v>40</v>
       </c>
       <c r="AN20" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO20" s="19">
         <v>1</v>
       </c>
       <c r="AP20" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ20" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AR20" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B21" s="19">
         <v>5</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D21" s="19">
         <v>3</v>
@@ -17197,7 +17197,7 @@
         <v>0.15289228116097112</v>
       </c>
       <c r="AB21" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AC21" s="19">
         <v>1344</v>
@@ -17229,30 +17229,30 @@
         <v>53</v>
       </c>
       <c r="AN21" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO21" s="19">
         <v>1</v>
       </c>
       <c r="AP21" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ21" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AR21" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B22" s="19">
         <v>6</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D22" s="19">
         <v>3</v>
@@ -17330,7 +17330,7 @@
         <v>0.18310932395707083</v>
       </c>
       <c r="AB22" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AC22" s="19">
         <v>1332</v>
@@ -17362,30 +17362,30 @@
         <v>74</v>
       </c>
       <c r="AN22" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO22" s="19">
         <v>1</v>
       </c>
       <c r="AP22" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ22" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AR22" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B23" s="19">
         <v>7</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D23" s="19">
         <v>3</v>
@@ -17463,7 +17463,7 @@
         <v>0.18709555853001333</v>
       </c>
       <c r="AB23" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AC23" s="19">
         <v>1225</v>
@@ -17491,30 +17491,30 @@
         <v>78</v>
       </c>
       <c r="AN23" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO23" s="19">
         <v>0</v>
       </c>
       <c r="AP23" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ23" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AR23" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B24" s="19">
         <v>8</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D24" s="19">
         <v>3</v>
@@ -17602,24 +17602,24 @@
       <c r="AN24" s="19"/>
       <c r="AO24" s="19"/>
       <c r="AP24" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ24" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AR24" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B25" s="19">
         <v>9</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D25" s="19">
         <v>3</v>
@@ -17695,24 +17695,24 @@
       <c r="AN25" s="19"/>
       <c r="AO25" s="19"/>
       <c r="AP25" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ25" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AR25" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B26" s="19">
         <v>10</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D26" s="19">
         <v>3</v>
@@ -17788,24 +17788,24 @@
       <c r="AN26" s="19"/>
       <c r="AO26" s="19"/>
       <c r="AP26" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ26" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AR26" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B27" s="19">
         <v>11</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D27" s="19">
         <v>3</v>
@@ -17881,18 +17881,18 @@
       <c r="AN27" s="19"/>
       <c r="AO27" s="19"/>
       <c r="AP27" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AQ27" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AR27" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="54" t="s">
-        <v>202</v>
+      <c r="A28" s="58" t="s">
+        <v>201</v>
       </c>
       <c r="B28" s="55"/>
       <c r="C28" s="55"/>
@@ -17911,7 +17911,7 @@
       <c r="P28" s="55"/>
       <c r="Q28" s="55"/>
       <c r="R28" s="55"/>
-      <c r="S28" s="56"/>
+      <c r="S28" s="60"/>
       <c r="T28" s="55"/>
       <c r="U28" s="55"/>
       <c r="V28" s="55"/>
@@ -17940,13 +17940,13 @@
     </row>
     <row r="29" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A29" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B29" s="19">
         <v>1</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D29" s="19">
         <v>1</v>
@@ -18029,13 +18029,13 @@
     </row>
     <row r="30" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A30" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B30" s="19">
         <v>2</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D30" s="19">
         <v>1</v>
@@ -18111,7 +18111,7 @@
         <v>0.14536975196660556</v>
       </c>
       <c r="AB30" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC30" s="19">
         <v>642</v>
@@ -18135,7 +18135,7 @@
         <v>28</v>
       </c>
       <c r="AN30" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO30" s="19">
         <v>0</v>
@@ -18146,13 +18146,13 @@
     </row>
     <row r="31" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A31" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B31" s="19">
         <v>3</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D31" s="19">
         <v>1</v>
@@ -18228,7 +18228,7 @@
         <v>7.4604726513432404E-2</v>
       </c>
       <c r="AB31" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC31" s="19">
         <v>1216</v>
@@ -18254,7 +18254,7 @@
         <v>27</v>
       </c>
       <c r="AN31" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO31" s="19">
         <v>0</v>
@@ -18265,13 +18265,13 @@
     </row>
     <row r="32" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A32" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B32" s="19">
         <v>4</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D32" s="19">
         <v>1</v>
@@ -18347,7 +18347,7 @@
         <v>7.6637686151174167E-2</v>
       </c>
       <c r="AB32" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC32" s="19">
         <v>1151</v>
@@ -18373,7 +18373,7 @@
         <v>27</v>
       </c>
       <c r="AN32" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO32" s="19">
         <v>0</v>
@@ -18384,13 +18384,13 @@
     </row>
     <row r="33" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A33" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B33" s="19">
         <v>5</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D33" s="19">
         <v>1</v>
@@ -18466,7 +18466,7 @@
         <v>9.9392779046470786E-2</v>
       </c>
       <c r="AB33" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC33" s="19">
         <v>831</v>
@@ -18490,7 +18490,7 @@
         <v>28</v>
       </c>
       <c r="AN33" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO33" s="19">
         <v>0</v>
@@ -18501,13 +18501,13 @@
     </row>
     <row r="34" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A34" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B34" s="19">
         <v>6</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D34" s="19">
         <v>1</v>
@@ -18583,7 +18583,7 @@
         <v>0.14801444043321299</v>
       </c>
       <c r="AB34" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC34" s="19">
         <v>554</v>
@@ -18605,7 +18605,7 @@
         <v>28</v>
       </c>
       <c r="AN34" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO34" s="19">
         <v>0</v>
@@ -18616,13 +18616,13 @@
     </row>
     <row r="35" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A35" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B35" s="19">
         <v>7</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D35" s="19">
         <v>1</v>
@@ -18698,7 +18698,7 @@
         <v>0.21980252225333388</v>
       </c>
       <c r="AB35" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC35" s="19">
         <v>340</v>
@@ -18720,7 +18720,7 @@
         <v>28</v>
       </c>
       <c r="AN35" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO35" s="19">
         <v>0</v>
@@ -18731,13 +18731,13 @@
     </row>
     <row r="36" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A36" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B36" s="19">
         <v>8</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D36" s="19">
         <v>1</v>
@@ -18813,7 +18813,7 @@
         <v>0.11008204011352422</v>
       </c>
       <c r="AB36" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC36" s="19">
         <v>240</v>
@@ -18835,7 +18835,7 @@
         <v>28</v>
       </c>
       <c r="AN36" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO36" s="19">
         <v>0</v>
@@ -18846,13 +18846,13 @@
     </row>
     <row r="37" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A37" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B37" s="19">
         <v>9</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D37" s="19">
         <v>1</v>
@@ -18928,7 +18928,7 @@
         <v>0.15811388300841897</v>
       </c>
       <c r="AB37" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC37" s="19">
         <v>100</v>
@@ -18950,7 +18950,7 @@
         <v>28</v>
       </c>
       <c r="AN37" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO37" s="19">
         <v>0</v>
@@ -18961,13 +18961,13 @@
     </row>
     <row r="38" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A38" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B38" s="19">
         <v>10</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D38" s="19">
         <v>1</v>
@@ -19018,7 +19018,7 @@
         <v>0.22919</v>
       </c>
       <c r="T38" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="U38" s="19" t="str">
         <f t="shared" si="22"/>
@@ -19043,7 +19043,7 @@
         <v>0</v>
       </c>
       <c r="AB38" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AC38" s="19">
         <v>41</v>
@@ -19061,7 +19061,7 @@
         <v>28</v>
       </c>
       <c r="AN38" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO38" s="19">
         <v>0</v>
@@ -19072,13 +19072,13 @@
     </row>
     <row r="39" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A39" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B39" s="19">
         <v>11</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D39" s="19">
         <v>1</v>
@@ -19129,7 +19129,7 @@
         <v>0.12725</v>
       </c>
       <c r="T39" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="U39" s="19" t="str">
         <f t="shared" si="22"/>
@@ -19154,7 +19154,7 @@
         <v>0</v>
       </c>
       <c r="AB39" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AC39" s="19">
         <v>25</v>
@@ -19172,7 +19172,7 @@
         <v>28</v>
       </c>
       <c r="AN39" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO39" s="19">
         <v>0</v>
@@ -19183,13 +19183,13 @@
     </row>
     <row r="40" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A40" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B40" s="19">
         <v>12</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D40" s="19">
         <v>1</v>
@@ -19240,7 +19240,7 @@
         <v>8.5859999999999992E-2</v>
       </c>
       <c r="T40" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="U40" s="19" t="str">
         <f t="shared" si="22"/>
@@ -19265,7 +19265,7 @@
         <v>0</v>
       </c>
       <c r="AB40" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AC40" s="19">
         <v>17</v>
@@ -19283,7 +19283,7 @@
         <v>28</v>
       </c>
       <c r="AN40" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO40" s="19">
         <v>0</v>
@@ -19327,8 +19327,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="58" t="s">
-        <v>79</v>
+      <c r="A1" s="57" t="s">
+        <v>78</v>
       </c>
       <c r="B1" s="55"/>
       <c r="C1" s="55"/>
@@ -19375,7 +19375,7 @@
       <c r="AR1" s="55"/>
     </row>
     <row r="2" spans="1:44" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="56" t="s">
         <v>27</v>
       </c>
       <c r="B2" s="55"/>
@@ -19385,21 +19385,21 @@
       <c r="F2" s="55"/>
       <c r="G2" s="55"/>
       <c r="H2" s="55"/>
-      <c r="I2" s="57" t="s">
-        <v>127</v>
+      <c r="I2" s="56" t="s">
+        <v>126</v>
       </c>
       <c r="J2" s="55"/>
       <c r="K2" s="55"/>
       <c r="L2" s="55"/>
       <c r="M2" s="55"/>
-      <c r="N2" s="57" t="s">
-        <v>128</v>
+      <c r="N2" s="56" t="s">
+        <v>127</v>
       </c>
       <c r="O2" s="55"/>
       <c r="P2" s="55"/>
       <c r="Q2" s="55"/>
-      <c r="R2" s="57" t="s">
-        <v>129</v>
+      <c r="R2" s="56" t="s">
+        <v>128</v>
       </c>
       <c r="S2" s="55"/>
       <c r="T2" s="55"/>
@@ -19409,8 +19409,8 @@
       <c r="X2" s="55"/>
       <c r="Y2" s="55"/>
       <c r="Z2" s="55"/>
-      <c r="AA2" s="57" t="s">
-        <v>130</v>
+      <c r="AA2" s="56" t="s">
+        <v>129</v>
       </c>
       <c r="AB2" s="55"/>
       <c r="AC2" s="55"/>
@@ -19423,32 +19423,32 @@
       <c r="AJ2" s="55"/>
       <c r="AK2" s="55"/>
       <c r="AL2" s="55"/>
-      <c r="AM2" s="57" t="s">
-        <v>131</v>
+      <c r="AM2" s="56" t="s">
+        <v>130</v>
       </c>
       <c r="AN2" s="55"/>
       <c r="AO2" s="55"/>
       <c r="AP2" s="55"/>
-      <c r="AQ2" s="57" t="s">
-        <v>132</v>
+      <c r="AQ2" s="56" t="s">
+        <v>131</v>
       </c>
       <c r="AR2" s="55"/>
     </row>
     <row r="3" spans="1:44" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>133</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>134</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>28</v>
       </c>
       <c r="D3" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>135</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>136</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>29</v>
@@ -19457,7 +19457,7 @@
         <v>30</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>31</v>
@@ -19469,16 +19469,16 @@
         <v>33</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M3" s="13" t="s">
         <v>6</v>
       </c>
       <c r="N3" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="O3" s="14" t="s">
         <v>139</v>
-      </c>
-      <c r="O3" s="14" t="s">
-        <v>140</v>
       </c>
       <c r="P3" s="14" t="s">
         <v>3</v>
@@ -19502,7 +19502,7 @@
         <v>38</v>
       </c>
       <c r="W3" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="X3" s="15" t="s">
         <v>5</v>
@@ -19511,66 +19511,66 @@
         <v>39</v>
       </c>
       <c r="Z3" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA3" s="49" t="s">
+        <v>258</v>
+      </c>
+      <c r="AB3" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="AA3" s="49" t="s">
+      <c r="AC3" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="AB3" s="16" t="s">
+      <c r="AD3" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE3" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF3" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG3" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH3" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI3" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="AJ3" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="AK3" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL3" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM3" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN3" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="AC3" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD3" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE3" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF3" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG3" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH3" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI3" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="AJ3" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK3" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="AL3" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AM3" s="17" t="s">
+      <c r="AO3" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="AP3" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="AQ3" s="18" t="s">
         <v>51</v>
-      </c>
-      <c r="AN3" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="AO3" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="AP3" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="AQ3" s="18" t="s">
-        <v>52</v>
       </c>
       <c r="AR3" s="18" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="59" t="s">
-        <v>203</v>
+      <c r="A4" s="54" t="s">
+        <v>202</v>
       </c>
       <c r="B4" s="55"/>
       <c r="C4" s="55"/>
@@ -19618,13 +19618,13 @@
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B5" s="19">
         <v>1</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D5" s="19">
         <v>3</v>
@@ -19702,7 +19702,7 @@
         <v>0.13453636291220758</v>
       </c>
       <c r="AB5" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC5" s="19">
         <v>1202</v>
@@ -19732,7 +19732,7 @@
         <v>25</v>
       </c>
       <c r="AN5" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO5" s="19">
         <v>0</v>
@@ -19743,13 +19743,13 @@
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B6" s="19">
         <v>2</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6" s="19">
         <v>3</v>
@@ -19827,7 +19827,7 @@
         <v>0.13443711203778075</v>
       </c>
       <c r="AB6" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC6" s="19">
         <v>1194</v>
@@ -19855,7 +19855,7 @@
         <v>25</v>
       </c>
       <c r="AN6" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO6" s="19">
         <v>0</v>
@@ -19866,13 +19866,13 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B7" s="19">
         <v>3</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D7" s="19">
         <v>3</v>
@@ -19950,7 +19950,7 @@
         <v>0.12130196279150954</v>
       </c>
       <c r="AB7" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC7" s="19">
         <v>1185</v>
@@ -19978,7 +19978,7 @@
         <v>25</v>
       </c>
       <c r="AN7" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO7" s="19">
         <v>0</v>
@@ -19989,13 +19989,13 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B8" s="19">
         <v>4</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D8" s="19">
         <v>3</v>
@@ -20073,7 +20073,7 @@
         <v>0.10989946578045898</v>
       </c>
       <c r="AB8" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC8" s="19">
         <v>1172</v>
@@ -20101,7 +20101,7 @@
         <v>24</v>
       </c>
       <c r="AN8" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO8" s="19">
         <v>0</v>
@@ -20112,13 +20112,13 @@
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B9" s="19">
         <v>5</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D9" s="19">
         <v>3</v>
@@ -20196,7 +20196,7 @@
         <v>0.10503514783016818</v>
       </c>
       <c r="AB9" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC9" s="19">
         <v>1154</v>
@@ -20222,7 +20222,7 @@
         <v>24</v>
       </c>
       <c r="AN9" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO9" s="19">
         <v>0</v>
@@ -20233,13 +20233,13 @@
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B10" s="19">
         <v>6</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10" s="19">
         <v>3</v>
@@ -20317,7 +20317,7 @@
         <v>0.10599798410900571</v>
       </c>
       <c r="AB10" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC10" s="19">
         <v>1137</v>
@@ -20345,7 +20345,7 @@
         <v>24</v>
       </c>
       <c r="AN10" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO10" s="19">
         <v>0</v>
@@ -20356,13 +20356,13 @@
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B11" s="19">
         <v>7</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D11" s="19">
         <v>3</v>
@@ -20440,7 +20440,7 @@
         <v>0.11198862759310788</v>
       </c>
       <c r="AB11" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC11" s="19">
         <v>1108</v>
@@ -20466,7 +20466,7 @@
         <v>24</v>
       </c>
       <c r="AN11" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO11" s="19">
         <v>0</v>
@@ -20477,13 +20477,13 @@
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B12" s="19">
         <v>8</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" s="19">
         <v>3</v>
@@ -20561,7 +20561,7 @@
         <v>0.11957337834496759</v>
       </c>
       <c r="AB12" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC12" s="19">
         <v>1060</v>
@@ -20587,7 +20587,7 @@
         <v>24</v>
       </c>
       <c r="AN12" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO12" s="19">
         <v>0</v>
@@ -20598,13 +20598,13 @@
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B13" s="19">
         <v>9</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" s="19">
         <v>3</v>
@@ -20682,7 +20682,7 @@
         <v>0.13871811234885648</v>
       </c>
       <c r="AB13" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC13" s="19">
         <v>907</v>
@@ -20710,7 +20710,7 @@
         <v>24</v>
       </c>
       <c r="AN13" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO13" s="19">
         <v>0</v>
@@ -20721,13 +20721,13 @@
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B14" s="19">
         <v>10</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" s="19">
         <v>3</v>
@@ -20805,7 +20805,7 @@
         <v>0.16292086998461311</v>
       </c>
       <c r="AB14" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AC14" s="19">
         <v>270</v>
@@ -20835,7 +20835,7 @@
         <v>24</v>
       </c>
       <c r="AN14" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO14" s="19">
         <v>0</v>
@@ -20846,13 +20846,13 @@
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B15" s="19">
         <v>11</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" s="19">
         <v>3</v>
@@ -20930,7 +20930,7 @@
         <v>0.27867981183435087</v>
       </c>
       <c r="AB15" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AC15" s="19">
         <v>102</v>
@@ -20954,20 +20954,20 @@
         <v>24</v>
       </c>
       <c r="AN15" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO15" s="19">
         <v>0</v>
       </c>
       <c r="AP15" s="19"/>
       <c r="AQ15" s="19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AR15" s="19"/>
     </row>
     <row r="16" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="61" t="s">
-        <v>204</v>
+      <c r="A16" s="59" t="s">
+        <v>203</v>
       </c>
       <c r="B16" s="55"/>
       <c r="C16" s="55"/>
@@ -21015,13 +21015,13 @@
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B17" s="19">
         <v>1</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D17" s="19">
         <v>3</v>
@@ -21099,7 +21099,7 @@
         <v>0.11568300150315967</v>
       </c>
       <c r="AB17" s="19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AC17" s="19">
         <v>1226</v>
@@ -21133,7 +21133,7 @@
         <v>51</v>
       </c>
       <c r="AN17" s="19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AO17" s="19"/>
       <c r="AP17" s="19"/>
@@ -21142,13 +21142,13 @@
     </row>
     <row r="18" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B18" s="19">
         <v>2</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D18" s="19">
         <v>3</v>
@@ -21226,7 +21226,7 @@
         <v>0.1140554873930934</v>
       </c>
       <c r="AB18" s="19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AC18" s="19">
         <v>1171</v>
@@ -21256,7 +21256,7 @@
         <v>50</v>
       </c>
       <c r="AN18" s="19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AO18" s="19"/>
       <c r="AP18" s="19"/>
@@ -21265,13 +21265,13 @@
     </row>
     <row r="19" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B19" s="19">
         <v>3</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D19" s="19">
         <v>3</v>
@@ -21349,7 +21349,7 @@
         <v>0.14732526759516404</v>
       </c>
       <c r="AB19" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC19" s="19">
         <v>785</v>
@@ -21377,7 +21377,7 @@
         <v>42</v>
       </c>
       <c r="AN19" s="19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AO19" s="19"/>
       <c r="AP19" s="19"/>
@@ -21386,13 +21386,13 @@
     </row>
     <row r="20" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B20" s="19">
         <v>4</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D20" s="19">
         <v>3</v>
@@ -21470,7 +21470,7 @@
         <v>8.3286400308663466E-2</v>
       </c>
       <c r="AB20" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC20" s="19">
         <v>596</v>
@@ -21505,13 +21505,13 @@
     </row>
     <row r="21" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A21" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B21" s="19">
         <v>5</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D21" s="19">
         <v>3</v>
@@ -21589,7 +21589,7 @@
         <v>0.10698715613988312</v>
       </c>
       <c r="AB21" s="19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AC21" s="19">
         <v>493</v>
@@ -21622,13 +21622,13 @@
     </row>
     <row r="22" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B22" s="19">
         <v>6</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D22" s="19">
         <v>3</v>
@@ -21706,7 +21706,7 @@
         <v>0.10320509993286058</v>
       </c>
       <c r="AB22" s="19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AC22" s="19">
         <v>386</v>
@@ -21741,13 +21741,13 @@
     </row>
     <row r="23" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B23" s="19">
         <v>7</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D23" s="19">
         <v>3</v>
@@ -21825,7 +21825,7 @@
         <v>0.14580820434638408</v>
       </c>
       <c r="AB23" s="19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AC23" s="19">
         <v>302</v>
@@ -21858,13 +21858,13 @@
     </row>
     <row r="24" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B24" s="19">
         <v>8</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D24" s="19">
         <v>3</v>
@@ -21942,7 +21942,7 @@
         <v>0.19225068260292394</v>
       </c>
       <c r="AB24" s="19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AC24" s="19">
         <v>223</v>
@@ -21975,13 +21975,13 @@
     </row>
     <row r="25" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B25" s="19">
         <v>9</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D25" s="19">
         <v>3</v>
@@ -22059,7 +22059,7 @@
         <v>0.25693450461934519</v>
       </c>
       <c r="AB25" s="19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AC25" s="19">
         <v>148</v>
@@ -22092,13 +22092,13 @@
     </row>
     <row r="26" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B26" s="19">
         <v>10</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D26" s="19">
         <v>3</v>
@@ -22176,7 +22176,7 @@
         <v>0.35647939958273855</v>
       </c>
       <c r="AB26" s="19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AC26" s="19">
         <v>76</v>
@@ -22209,13 +22209,13 @@
     </row>
     <row r="27" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B27" s="19">
         <v>11</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D27" s="19">
         <v>3</v>
@@ -22293,7 +22293,7 @@
         <v/>
       </c>
       <c r="AB27" s="19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AC27" s="19">
         <v>0</v>
@@ -22330,7 +22330,7 @@
     </row>
     <row r="28" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="63" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B28" s="55"/>
       <c r="C28" s="55"/>
@@ -22378,13 +22378,13 @@
     </row>
     <row r="29" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A29" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B29" s="19">
         <v>1</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D29" s="19">
         <v>3</v>
@@ -22466,7 +22466,7 @@
         <v>0.20775377298141626</v>
       </c>
       <c r="AB29" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC29" s="19">
         <v>1065</v>
@@ -22502,7 +22502,7 @@
         <v>30</v>
       </c>
       <c r="AN29" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO29" s="19">
         <v>1</v>
@@ -22513,13 +22513,13 @@
     </row>
     <row r="30" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A30" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B30" s="19">
         <v>2</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D30" s="19">
         <v>3</v>
@@ -22601,7 +22601,7 @@
         <v>0.11875544969222554</v>
       </c>
       <c r="AB30" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC30" s="19">
         <v>1777</v>
@@ -22635,7 +22635,7 @@
         <v>30</v>
       </c>
       <c r="AN30" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO30" s="19">
         <v>1</v>
@@ -22646,13 +22646,13 @@
     </row>
     <row r="31" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A31" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B31" s="19">
         <v>3</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D31" s="19">
         <v>3</v>
@@ -22734,7 +22734,7 @@
         <v>0.12594105026440022</v>
       </c>
       <c r="AB31" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC31" s="19">
         <v>1693</v>
@@ -22768,7 +22768,7 @@
         <v>29</v>
       </c>
       <c r="AN31" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO31" s="19">
         <v>1</v>
@@ -22776,18 +22776,18 @@
       <c r="AP31" s="19"/>
       <c r="AQ31" s="19"/>
       <c r="AR31" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A32" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B32" s="19">
         <v>4</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D32" s="19">
         <v>3</v>
@@ -22869,7 +22869,7 @@
         <v>0.13401066188099209</v>
       </c>
       <c r="AB32" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC32" s="19">
         <v>1611</v>
@@ -22901,7 +22901,7 @@
         <v>28</v>
       </c>
       <c r="AN32" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO32" s="19">
         <v>1</v>
@@ -22909,18 +22909,18 @@
       <c r="AP32" s="19"/>
       <c r="AQ32" s="19"/>
       <c r="AR32" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="33" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A33" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B33" s="19">
         <v>5</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D33" s="19">
         <v>3</v>
@@ -23002,7 +23002,7 @@
         <v>0.14316152258965364</v>
       </c>
       <c r="AB33" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC33" s="19">
         <v>1531</v>
@@ -23034,7 +23034,7 @@
         <v>27</v>
       </c>
       <c r="AN33" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO33" s="19">
         <v>0</v>
@@ -23045,13 +23045,13 @@
     </row>
     <row r="34" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A34" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B34" s="19">
         <v>6</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D34" s="19">
         <v>3</v>
@@ -23133,7 +23133,7 @@
         <v>0.14962830474253841</v>
       </c>
       <c r="AB34" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC34" s="19">
         <v>1461</v>
@@ -23165,7 +23165,7 @@
         <v>27</v>
       </c>
       <c r="AN34" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO34" s="19">
         <v>0</v>
@@ -23176,13 +23176,13 @@
     </row>
     <row r="35" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A35" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B35" s="19">
         <v>7</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D35" s="19">
         <v>3</v>
@@ -23264,7 +23264,7 @@
         <v>0.16391140615216035</v>
       </c>
       <c r="AB35" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AC35" s="19">
         <v>1315</v>
@@ -23298,7 +23298,7 @@
         <v>27</v>
       </c>
       <c r="AN35" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO35" s="19">
         <v>0</v>
@@ -23309,13 +23309,13 @@
     </row>
     <row r="36" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A36" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B36" s="19">
         <v>8</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D36" s="19">
         <v>3</v>
@@ -23397,7 +23397,7 @@
         <v>0.24536640788453373</v>
       </c>
       <c r="AB36" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AC36" s="19">
         <v>830</v>
@@ -23427,7 +23427,7 @@
         <v>28</v>
       </c>
       <c r="AN36" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO36" s="19">
         <v>0</v>
@@ -23438,13 +23438,13 @@
     </row>
     <row r="37" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A37" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B37" s="19">
         <v>9</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D37" s="19">
         <v>3</v>
@@ -23526,7 +23526,7 @@
         <v>0.39845719237686184</v>
       </c>
       <c r="AB37" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AC37" s="19">
         <v>472</v>
@@ -23556,7 +23556,7 @@
         <v>27</v>
       </c>
       <c r="AN37" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO37" s="19">
         <v>0</v>
@@ -23567,13 +23567,13 @@
     </row>
     <row r="38" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A38" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B38" s="19">
         <v>10</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D38" s="19">
         <v>3</v>
@@ -23655,7 +23655,7 @@
         <v>0.28621633358719645</v>
       </c>
       <c r="AB38" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AC38" s="19">
         <v>195</v>
@@ -23685,7 +23685,7 @@
         <v>27</v>
       </c>
       <c r="AN38" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO38" s="19">
         <v>0</v>
@@ -23696,13 +23696,13 @@
     </row>
     <row r="39" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A39" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B39" s="19">
         <v>11</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D39" s="19">
         <v>3</v>
@@ -23755,7 +23755,7 @@
         <v>1.4406E-2</v>
       </c>
       <c r="T39" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="U39" s="19" t="str">
         <f t="shared" si="22"/>
@@ -23784,7 +23784,7 @@
         <v>0.34084137000395481</v>
       </c>
       <c r="AB39" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AC39" s="19">
         <v>90</v>
@@ -23812,7 +23812,7 @@
         <v>26</v>
       </c>
       <c r="AN39" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO39" s="19">
         <v>0</v>
@@ -23823,7 +23823,7 @@
     </row>
     <row r="40" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="62" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B40" s="55"/>
       <c r="C40" s="55"/>
@@ -23871,13 +23871,13 @@
     </row>
     <row r="41" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A41" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B41" s="19">
         <v>1</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D41" s="19">
         <v>3</v>
@@ -23961,7 +23961,7 @@
         <v/>
       </c>
       <c r="AB41" s="19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AC41" s="19"/>
       <c r="AD41" s="19"/>
@@ -23977,7 +23977,7 @@
         <v>28</v>
       </c>
       <c r="AN41" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AO41" s="19">
         <v>1</v>
@@ -23985,18 +23985,18 @@
       <c r="AP41" s="19"/>
       <c r="AQ41" s="19"/>
       <c r="AR41" s="19" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="42" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A42" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B42" s="19">
         <v>2</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D42" s="19">
         <v>3</v>
@@ -24078,7 +24078,7 @@
         <v/>
       </c>
       <c r="AB42" s="19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AC42" s="19"/>
       <c r="AD42" s="19"/>
@@ -24094,7 +24094,7 @@
         <v>43</v>
       </c>
       <c r="AN42" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AO42" s="19">
         <v>1</v>
@@ -24102,18 +24102,18 @@
       <c r="AP42" s="19"/>
       <c r="AQ42" s="19"/>
       <c r="AR42" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="43" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A43" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B43" s="19">
         <v>3</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D43" s="19">
         <v>3</v>
@@ -24197,7 +24197,7 @@
         <v/>
       </c>
       <c r="AB43" s="19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AC43" s="19"/>
       <c r="AD43" s="19"/>
@@ -24213,7 +24213,7 @@
         <v>32</v>
       </c>
       <c r="AN43" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO43" s="19">
         <v>1</v>
@@ -24221,18 +24221,18 @@
       <c r="AP43" s="19"/>
       <c r="AQ43" s="19"/>
       <c r="AR43" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="44" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A44" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B44" s="19">
         <v>4</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D44" s="19">
         <v>3</v>
@@ -24316,7 +24316,7 @@
         <v/>
       </c>
       <c r="AB44" s="19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AC44" s="19"/>
       <c r="AD44" s="19"/>
@@ -24332,7 +24332,7 @@
         <v>33</v>
       </c>
       <c r="AN44" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO44" s="19">
         <v>1</v>
@@ -24340,18 +24340,18 @@
       <c r="AP44" s="19"/>
       <c r="AQ44" s="19"/>
       <c r="AR44" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="45" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A45" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B45" s="19">
         <v>5</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D45" s="19">
         <v>3</v>
@@ -24435,7 +24435,7 @@
         <v/>
       </c>
       <c r="AB45" s="19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AC45" s="19"/>
       <c r="AD45" s="19"/>
@@ -24451,7 +24451,7 @@
         <v>37</v>
       </c>
       <c r="AN45" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AO45" s="19">
         <v>1</v>
@@ -24459,18 +24459,18 @@
       <c r="AP45" s="19"/>
       <c r="AQ45" s="19"/>
       <c r="AR45" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="46" spans="1:44" x14ac:dyDescent="0.3">
       <c r="A46" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B46" s="19">
         <v>6</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D46" s="19">
         <v>3</v>
@@ -24554,7 +24554,7 @@
         <v/>
       </c>
       <c r="AB46" s="19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AC46" s="19"/>
       <c r="AD46" s="19"/>
@@ -24570,7 +24570,7 @@
         <v>42</v>
       </c>
       <c r="AN46" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AO46" s="19">
         <v>1</v>
@@ -24578,7 +24578,7 @@
       <c r="AP46" s="19"/>
       <c r="AQ46" s="19"/>
       <c r="AR46" s="19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -24616,7 +24616,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -24630,7 +24630,7 @@
     </row>
     <row r="2" spans="1:10" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>0</v>
@@ -24639,13 +24639,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E2" s="29" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G2" s="30" t="s">
         <v>3</v>
@@ -24982,18 +24982,18 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G20" s="10"/>
       <c r="H20" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I20" s="10"/>
     </row>
@@ -25007,7 +25007,7 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
@@ -25017,7 +25017,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
@@ -25027,7 +25027,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B28" t="s">
         <v>11</v>
@@ -25035,7 +25035,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B29" t="s">
         <v>12</v>
@@ -25043,7 +25043,7 @@
     </row>
     <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="32" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B31" s="33"/>
       <c r="C31" s="33"/>
@@ -25057,7 +25057,7 @@
     </row>
     <row r="32" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="27" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B32" s="28" t="s">
         <v>0</v>
@@ -25066,13 +25066,13 @@
         <v>1</v>
       </c>
       <c r="D32" s="28" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E32" s="29" t="s">
         <v>2</v>
       </c>
       <c r="F32" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G32" s="30" t="s">
         <v>3</v>
@@ -25585,22 +25585,22 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>220</v>
+      </c>
+      <c r="D49" t="s">
         <v>221</v>
-      </c>
-      <c r="D49" t="s">
-        <v>222</v>
       </c>
       <c r="E49" s="37">
         <v>46213</v>
       </c>
       <c r="F49" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G49" s="38">
         <v>27</v>
       </c>
       <c r="H49" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
@@ -25610,7 +25610,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
@@ -25620,7 +25620,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
@@ -25630,7 +25630,7 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B55" t="s">
         <v>11</v>
@@ -25638,7 +25638,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B56" t="s">
         <v>12</v>
@@ -25646,7 +25646,7 @@
     </row>
     <row r="58" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="40" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B58" s="25"/>
       <c r="C58" s="25"/>
@@ -25660,7 +25660,7 @@
     </row>
     <row r="59" spans="1:10" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="41" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B59" s="42" t="s">
         <v>0</v>
@@ -25669,13 +25669,13 @@
         <v>1</v>
       </c>
       <c r="D59" s="42" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E59" s="43" t="s">
         <v>2</v>
       </c>
       <c r="F59" s="44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G59" s="44" t="s">
         <v>3</v>
@@ -26193,22 +26193,22 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D77" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="E77" s="39">
         <v>46213</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G77" s="10">
         <v>26</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I77" s="10"/>
     </row>
@@ -26222,7 +26222,7 @@
         <v>15</v>
       </c>
       <c r="B79" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
@@ -26232,7 +26232,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
@@ -26242,7 +26242,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B85" t="s">
         <v>11</v>
@@ -26250,7 +26250,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B86" t="s">
         <v>12</v>
@@ -26281,7 +26281,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B1" s="34"/>
       <c r="C1" s="34"/>
@@ -26300,24 +26300,24 @@
     </row>
     <row r="2" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="C2" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="D2" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="E2" s="30" t="s">
         <v>237</v>
-      </c>
-      <c r="E2" s="30" t="s">
-        <v>238</v>
       </c>
       <c r="F2" s="29"/>
       <c r="G2" s="29"/>
       <c r="H2" s="28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I2" s="29" t="s">
         <v>2</v>
@@ -26351,7 +26351,7 @@
         <v>29</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
@@ -26376,7 +26376,7 @@
         <v>29</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
@@ -26401,7 +26401,7 @@
         <v>28</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
@@ -26426,7 +26426,7 @@
         <v>33</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -26451,7 +26451,7 @@
         <v>29</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
@@ -26471,7 +26471,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B9" s="21">
         <f>IF(COUNT(B3:B7)=0,"",IFERROR(AVERAGE(B3:B7),""))</f>
@@ -26490,7 +26490,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B10" s="21">
         <f>IF(COUNT(B3:B7)&lt;2,"",IFERROR(STDEV(B3:B7),""))</f>
@@ -26509,7 +26509,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" s="21">
         <f>IF(COUNT(B3:B7)&lt;2,"",IFERROR(B10/B9*100,""))</f>
@@ -26539,7 +26539,7 @@
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="32" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B14" s="34"/>
       <c r="C14" s="34"/>
@@ -26558,49 +26558,49 @@
     </row>
     <row r="15" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="C15" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="D15" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="30" t="s">
+      <c r="E15" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="G15" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="E15" s="30" t="s">
-        <v>245</v>
-      </c>
-      <c r="F15" s="30" t="s">
+      <c r="H15" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="I15" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="J15" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="K15" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="L15" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="M15" s="31" t="s">
         <v>246</v>
       </c>
-      <c r="G15" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="H15" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="I15" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="J15" s="31" t="s">
-        <v>88</v>
-      </c>
-      <c r="K15" s="31" t="s">
-        <v>89</v>
-      </c>
-      <c r="L15" s="31" t="s">
+      <c r="N15" s="31" t="s">
+        <v>247</v>
+      </c>
+      <c r="O15" s="31" t="s">
         <v>90</v>
-      </c>
-      <c r="M15" s="31" t="s">
-        <v>247</v>
-      </c>
-      <c r="N15" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="O15" s="31" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -26877,7 +26877,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B22" s="22"/>
       <c r="C22" s="22"/>
@@ -26946,7 +26946,7 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="64" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B1" s="55"/>
       <c r="C1" s="55"/>
@@ -26975,76 +26975,76 @@
     </row>
     <row r="2" spans="1:25" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C2" s="20" t="s">
         <v>28</v>
       </c>
       <c r="D2" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="E2" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="F2" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="H2" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="G2" s="20" t="s">
-        <v>252</v>
-      </c>
-      <c r="H2" s="20" t="s">
+      <c r="I2" s="20" t="s">
         <v>95</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>96</v>
       </c>
       <c r="J2" s="20" t="s">
         <v>6</v>
       </c>
       <c r="K2" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="L2" s="20" t="s">
         <v>97</v>
-      </c>
-      <c r="L2" s="20" t="s">
-        <v>98</v>
       </c>
       <c r="M2" s="20" t="s">
         <v>3</v>
       </c>
       <c r="N2" s="20" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O2" s="20" t="s">
         <v>37</v>
       </c>
       <c r="P2" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q2" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="Q2" s="20" t="s">
+      <c r="R2" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="R2" s="20" t="s">
+      <c r="S2" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="T2" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="U2" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="V2" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="W2" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="S2" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="T2" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="U2" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="V2" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="W2" s="20" t="s">
+      <c r="X2" s="20" t="s">
         <v>257</v>
-      </c>
-      <c r="X2" s="20" t="s">
-        <v>258</v>
       </c>
       <c r="Y2" s="20" t="s">
         <v>2</v>
